--- a/data/AjustesPostFacturacion.xlsx
+++ b/data/AjustesPostFacturacion.xlsx
@@ -106,7 +106,7 @@
     <t>Carlos Alberto Mendoza Solís</t>
   </si>
   <si>
-    <t>Corporación Minera del Sur S.A.C.</t>
+    <t>Corporación Minera Pampa Azul S.A.C.</t>
   </si>
   <si>
     <t>Roberto Alonso Chávez Ramos</t>
